--- a/assets/AcrossTheWall.xlsx
+++ b/assets/AcrossTheWall.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12200"/>
+    <workbookView windowWidth="23040" windowHeight="11360"/>
   </bookViews>
   <sheets>
     <sheet name="AcrossTheWall" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="73">
   <si>
     <t>question-room</t>
   </si>
@@ -318,6 +318,12 @@
     <t>Four people live in different coloured houses, determine who lives in each house below:</t>
   </si>
   <si>
+    <t>Houses</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
     <t>Chris,Bob,Anna,David</t>
   </si>
   <si>
@@ -325,9 +331,6 @@
   </si>
   <si>
     <t>multiple-choice</t>
-  </si>
-  <si>
-    <t>image</t>
   </si>
   <si>
     <t>Pineapple</t>
@@ -2044,10 +2047,10 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="F16" t="s">
         <v>27</v>
@@ -2059,7 +2062,7 @@
         <v>4</v>
       </c>
       <c r="K16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -2070,25 +2073,25 @@
         <v>300</v>
       </c>
       <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" t="s">
         <v>52</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" t="s">
-        <v>54</v>
       </c>
       <c r="K17" t="s">
         <v>13</v>
       </c>
       <c r="L17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -2099,25 +2102,25 @@
         <v>300</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K18" t="s">
         <v>11</v>
       </c>
       <c r="L18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -2128,25 +2131,25 @@
         <v>300</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F19" t="s">
         <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J19">
         <v>3</v>
       </c>
       <c r="K19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -2157,34 +2160,34 @@
         <v>300</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K20" t="s">
         <v>12</v>
       </c>
       <c r="L20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
